--- a/ch_05_statistical_testing_inference/ch_05_solution.xlsx
+++ b/ch_05_statistical_testing_inference/ch_05_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30014"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_05_statistical_testing_inference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1E1D74-DF22-4CDB-83B2-53B0FDE77034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5A7E4B-3F58-4939-933C-5432E4823721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -52,6 +52,13 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
@@ -59,21 +66,14 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
+          <xlrd:rvb i="3"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="6"/>
+          <xlrd:rvb i="4"/>
         </ext>
       </extLst>
     </bk>
@@ -1433,171 +1433,29 @@
 </rvTypesInfo>
 </file>
 
-<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
-  <a r="12" c="10">
-    <v t="s"/>
-    <v t="s">mpg</v>
-    <v t="s">cylinders</v>
-    <v t="s">displacement</v>
-    <v t="s">horsepower</v>
-    <v t="s">weight</v>
-    <v t="s">acceleration</v>
-    <v t="s">model_year</v>
-    <v t="s">origin</v>
-    <v t="s">name</v>
-    <v>0</v>
-    <v>18</v>
-    <v>8</v>
-    <v>307</v>
-    <v>130</v>
-    <v>3504</v>
-    <v>12</v>
-    <v>70</v>
-    <v t="s">usa</v>
-    <v t="s">chevrolet chevelle malibu</v>
-    <v>1</v>
-    <v>15</v>
-    <v>8</v>
-    <v>350</v>
-    <v>165</v>
-    <v>3693</v>
-    <v>11.5</v>
-    <v>70</v>
-    <v t="s">usa</v>
-    <v t="s">buick skylark 320</v>
-    <v>2</v>
-    <v>18</v>
-    <v>8</v>
-    <v>318</v>
-    <v>150</v>
-    <v>3436</v>
-    <v>11</v>
-    <v>70</v>
-    <v t="s">usa</v>
-    <v t="s">plymouth satellite</v>
-    <v>3</v>
-    <v>16</v>
-    <v>8</v>
-    <v>304</v>
-    <v>150</v>
-    <v>3433</v>
-    <v>12</v>
-    <v>70</v>
-    <v t="s">usa</v>
-    <v t="s">amc rebel sst</v>
-    <v>4</v>
-    <v>17</v>
-    <v>8</v>
-    <v>302</v>
-    <v>140</v>
-    <v>3449</v>
-    <v>10.5</v>
-    <v>70</v>
-    <v t="s">usa</v>
-    <v t="s">ford torino</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v>393</v>
-    <v>27</v>
-    <v>4</v>
-    <v>140</v>
-    <v>86</v>
-    <v>2790</v>
-    <v>15.6</v>
-    <v>82</v>
-    <v t="s">usa</v>
-    <v t="s">ford mustang gl</v>
-    <v>394</v>
-    <v>44</v>
-    <v>4</v>
-    <v>97</v>
-    <v>52</v>
-    <v>2130</v>
-    <v>24.6</v>
-    <v>82</v>
-    <v t="s">europe</v>
-    <v t="s">vw pickup</v>
-    <v>395</v>
-    <v>32</v>
-    <v>4</v>
-    <v>135</v>
-    <v>84</v>
-    <v>2295</v>
-    <v>11.6</v>
-    <v>82</v>
-    <v t="s">usa</v>
-    <v t="s">dodge rampage</v>
-    <v>396</v>
-    <v>28</v>
-    <v>4</v>
-    <v>120</v>
-    <v>79</v>
-    <v>2625</v>
-    <v>18.600000000000001</v>
-    <v>82</v>
-    <v t="s">usa</v>
-    <v t="s">ford ranger</v>
-    <v>397</v>
-    <v>31</v>
-    <v>4</v>
-    <v>119</v>
-    <v>82</v>
-    <v>2720</v>
-    <v>19.399999999999999</v>
-    <v>82</v>
-    <v t="s">usa</v>
-    <v t="s">chevy s-10</v>
-  </a>
-</arrayData>
-</file>
-
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <rv s="0">
-    <v>0</v>
+    <v>14</v>
   </rv>
   <rv s="1">
-    <v>DataFrame</v>
-    <v>1</v>
+    <fb>0</fb>
     <v>0</v>
-  </rv>
-  <rv s="2">
-    <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
-    <v>DataFrame</v>
-    <v xml:space="preserve">      mpg  cylinders  displacement  horsepower  weight  acceleration  \
-0    18.0          8         307.0       130.0    3504          12.0   
-1    15.0          8         350.0       165.0    3693          11.5   
-2    18.0          8         318.0  ...</v>
-    <v>1</v>
-    <v>2</v>
-  </rv>
-  <rv s="3">
-    <fb>0</fb>
-    <v>3</v>
   </rv>
   <rv s="2">
     <fb>0</fb>
     <v>&lt;class 'NoneType'&gt;</v>
     <v>NoneType</v>
     <v>None</v>
-    <v>3</v>
-    <v>2</v>
+    <v>1</v>
+    <v>1</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>0</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>1</v>
     <v>9</v>
     <v>Image generated by Python</v>
@@ -1606,14 +1464,12 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
-  <s t="_array">
-    <k n="array" t="a"/>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+  <s t="_error">
+    <k n="errorType" t="i"/>
   </s>
-  <s t="_entity">
-    <k n="_DisplayString" t="s"/>
-    <k n="_ViewInfo" t="spb"/>
-    <k n="arrayPreview" t="r"/>
+  <s t="_formattednumber">
+    <k n="_Format" t="spb"/>
   </s>
   <s t="_python">
     <k n="Python_type" t="s"/>
@@ -1621,9 +1477,6 @@
     <k n="Python_str" t="s"/>
     <k n="preview" t="r"/>
     <k n="_Provider" t="spb"/>
-  </s>
-  <s t="_formattednumber">
-    <k n="_Format" t="spb"/>
   </s>
   <s t="_localImage">
     <k n="_rvRel:LocalImageIdentifier" t="i"/>
@@ -1635,48 +1488,28 @@
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbData count="4">
+  <spbData count="2">
     <spb s="0">
-      <v>398</v>
-      <v>9</v>
-      <v>DataFrame</v>
-      <v>arrayPreview</v>
       <v>1</v>
     </spb>
     <spb s="1">
-      <v>0</v>
-    </spb>
-    <spb s="2">
       <v>https://www.anaconda.com/excel</v>
       <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
       <v>Python provided by Anaconda</v>
-    </spb>
-    <spb s="3">
-      <v>1</v>
     </spb>
   </spbData>
 </supportingPropertyBags>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="4">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="2">
   <s>
-    <k n="drw" t="i"/>
-    <k n="dcol" t="i"/>
-    <k n="name" t="s"/>
-    <k n="array" t="s"/>
-    <k n="headers" t="b"/>
-  </s>
-  <s>
-    <k n="ArrayCardInfo" t="spb"/>
+    <k n="_Self" t="i"/>
   </s>
   <s>
     <k n="link" t="s"/>
     <k n="logo" t="s"/>
     <k n="name" t="s"/>
-  </s>
-  <s>
-    <k n="_Self" t="i"/>
   </s>
 </spbStructures>
 </file>
@@ -2048,9 +1881,9 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="e" cm="1" vm="1">
-        <f t="array" ref="K1">_xlfn._xlws.PY(0,1,mpg[#All])</f>
-        <v>#VALUE!</v>
+      <c r="K1" cm="1">
+        <f t="array" aca="1" ref="K1" ca="1">_xlfn._xlws.PY(0,1,mpg[#All])</f>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.5">
@@ -13602,147 +13435,191 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A1" t="str" cm="1">
-        <f t="array" ref="A1:I5">_xlfn._xlws.PY(1,0)</f>
+        <f t="array" aca="1" ref="A1:I5" ca="1">_xlfn._xlws.PY(1,0)</f>
         <v/>
       </c>
       <c r="B1" t="str">
+        <f ca="1"/>
         <v>count</v>
       </c>
       <c r="C1" s="1" t="str">
+        <f ca="1"/>
         <v>mean</v>
       </c>
       <c r="D1" s="1" t="str">
+        <f ca="1"/>
         <v>std</v>
       </c>
       <c r="E1" s="1" t="str">
+        <f ca="1"/>
         <v>min</v>
       </c>
       <c r="F1" s="1" t="str">
+        <f ca="1"/>
         <v>25%</v>
       </c>
       <c r="G1" s="1" t="str">
+        <f ca="1"/>
         <v>50%</v>
       </c>
       <c r="H1" s="1" t="str">
+        <f ca="1"/>
         <v>75%</v>
       </c>
       <c r="I1" s="1" t="str">
+        <f ca="1"/>
         <v>max</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A2" t="str">
+        <f ca="1"/>
         <v>origin</v>
       </c>
       <c r="B2" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="C2" s="1" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="D2" s="1" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="E2" s="1" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="F2" s="1" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="G2" s="1" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="H2" s="1" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="I2" s="1" t="str">
+        <f ca="1"/>
         <v/>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" t="str">
+        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B3">
+        <f ca="1"/>
         <v>70</v>
       </c>
       <c r="C3" s="1">
+        <f ca="1"/>
         <v>27.89142857142857</v>
       </c>
       <c r="D3" s="1">
+        <f ca="1"/>
         <v>6.7239296407431706</v>
       </c>
       <c r="E3" s="1">
+        <f ca="1"/>
         <v>16.2</v>
       </c>
       <c r="F3" s="1">
+        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="G3" s="1">
+        <f ca="1"/>
         <v>26.5</v>
       </c>
       <c r="H3" s="1">
+        <f ca="1"/>
         <v>30.65</v>
       </c>
       <c r="I3" s="1">
+        <f ca="1"/>
         <v>44.3</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A4" t="str">
+        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B4">
+        <f ca="1"/>
         <v>79</v>
       </c>
       <c r="C4" s="1">
+        <f ca="1"/>
         <v>30.450632911392404</v>
       </c>
       <c r="D4" s="1">
+        <f ca="1"/>
         <v>6.0900480697383239</v>
       </c>
       <c r="E4" s="1">
+        <f ca="1"/>
         <v>18</v>
       </c>
       <c r="F4" s="1">
+        <f ca="1"/>
         <v>25.7</v>
       </c>
       <c r="G4" s="1">
+        <f ca="1"/>
         <v>31.6</v>
       </c>
       <c r="H4" s="1">
+        <f ca="1"/>
         <v>34.049999999999997</v>
       </c>
       <c r="I4" s="1">
+        <f ca="1"/>
         <v>46.6</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A5" t="str">
+        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="B5">
+        <f ca="1"/>
         <v>249</v>
       </c>
       <c r="C5" s="1">
+        <f ca="1"/>
         <v>20.083534136546184</v>
       </c>
       <c r="D5" s="1">
+        <f ca="1"/>
         <v>6.4028920160496918</v>
       </c>
       <c r="E5" s="1">
+        <f ca="1"/>
         <v>9</v>
       </c>
       <c r="F5" s="1">
+        <f ca="1"/>
         <v>15</v>
       </c>
       <c r="G5" s="1">
+        <f ca="1"/>
         <v>18.5</v>
       </c>
       <c r="H5" s="1">
+        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="I5" s="1">
+        <f ca="1"/>
         <v>39</v>
       </c>
     </row>
@@ -13757,501 +13634,627 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A8" t="str" cm="1">
-        <f t="array" ref="A8:E9">_xlfn._xlws.PY(2,0)</f>
+        <f t="array" aca="1" ref="A8:E9" ca="1">_xlfn._xlws.PY(2,0)</f>
         <v>Test statistic</v>
       </c>
       <c r="B8" t="str">
+        <f ca="1"/>
         <v>p-value</v>
       </c>
       <c r="C8" t="str">
+        <f ca="1"/>
         <v>Asia mean</v>
       </c>
       <c r="D8" t="str">
+        <f ca="1"/>
         <v>Europe mean</v>
       </c>
       <c r="E8" t="str">
+        <f ca="1"/>
         <v>Difference</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A9">
+        <f ca="1"/>
         <v>2.4378000000000002</v>
       </c>
       <c r="B9">
+        <f ca="1"/>
         <v>1.6E-2</v>
       </c>
       <c r="C9">
+        <f ca="1"/>
         <v>30.45</v>
       </c>
       <c r="D9">
+        <f ca="1"/>
         <v>27.89</v>
       </c>
       <c r="E9">
+        <f ca="1"/>
         <v>2.56</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A12" t="str" cm="1">
-        <f t="array" ref="A12">_xlfn._xlws.PY(3,0)</f>
+        <f t="array" aca="1" ref="A12" ca="1">_xlfn._xlws.PY(3,0)</f>
         <v>Cohen's d (effect size): 0.4002</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A14" t="str" cm="1">
-        <f t="array" ref="A14:E15">_xlfn._xlws.PY(4,0)</f>
+        <f t="array" aca="1" ref="A14:E15" ca="1">_xlfn._xlws.PY(4,0)</f>
         <v>F-statistic</v>
       </c>
       <c r="B14" t="str">
+        <f ca="1"/>
         <v>p-value</v>
       </c>
       <c r="C14" t="str">
+        <f ca="1"/>
         <v>USA mean</v>
       </c>
       <c r="D14" t="str">
+        <f ca="1"/>
         <v>Europe mean</v>
       </c>
       <c r="E14" t="str">
+        <f ca="1"/>
         <v>Japan mean</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A15">
+        <f ca="1"/>
         <v>98.54</v>
       </c>
       <c r="B15" t="str">
+        <f ca="1"/>
         <v>0.0</v>
       </c>
       <c r="C15">
+        <f ca="1"/>
         <v>20.079999999999998</v>
       </c>
       <c r="D15">
+        <f ca="1"/>
         <v>27.89</v>
       </c>
       <c r="E15">
+        <f ca="1"/>
         <v>30.45</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A17" t="str" cm="1">
-        <f t="array" ref="A17:G20">_xlfn._xlws.PY(5,0)</f>
+        <f t="array" aca="1" ref="A17:G20" ca="1">_xlfn._xlws.PY(5,0)</f>
         <v>group1</v>
       </c>
       <c r="B17" t="str">
+        <f ca="1"/>
         <v>group2</v>
       </c>
       <c r="C17" t="str">
+        <f ca="1"/>
         <v>meandiff</v>
       </c>
       <c r="D17" t="str">
+        <f ca="1"/>
         <v>p-adj</v>
       </c>
       <c r="E17" t="str">
+        <f ca="1"/>
         <v>lower</v>
       </c>
       <c r="F17" t="str">
+        <f ca="1"/>
         <v>upper</v>
       </c>
       <c r="G17" t="str">
+        <f ca="1"/>
         <v>reject</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A18" t="str">
+        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B18" t="str">
+        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="C18">
+        <f ca="1"/>
         <v>2.5592000000000001</v>
       </c>
       <c r="D18">
+        <f ca="1"/>
         <v>4.0399999999999998E-2</v>
       </c>
       <c r="E18">
+        <f ca="1"/>
         <v>8.77E-2</v>
       </c>
       <c r="F18">
+        <f ca="1"/>
         <v>5.0307000000000004</v>
       </c>
       <c r="G18" t="b">
+        <f ca="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A19" t="str">
+        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B19" t="str">
+        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="C19">
+        <f ca="1"/>
         <v>-7.8079000000000001</v>
       </c>
       <c r="D19">
+        <f ca="1"/>
         <v>0</v>
       </c>
       <c r="E19">
+        <f ca="1"/>
         <v>-9.8447999999999993</v>
       </c>
       <c r="F19">
+        <f ca="1"/>
         <v>-5.7709999999999999</v>
       </c>
       <c r="G19" t="b">
+        <f ca="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A20" t="str">
+        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B20" t="str">
+        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="C20">
+        <f ca="1"/>
         <v>-10.367100000000001</v>
       </c>
       <c r="D20">
+        <f ca="1"/>
         <v>0</v>
       </c>
       <c r="E20">
+        <f ca="1"/>
         <v>-12.311400000000001</v>
       </c>
       <c r="F20">
+        <f ca="1"/>
         <v>-8.4228000000000005</v>
       </c>
       <c r="G20" t="b">
+        <f ca="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A23" t="str" cm="1">
-        <f t="array" ref="A23:D32">_xlfn._xlws.PY(6,0)</f>
+        <f t="array" aca="1" ref="A23:D32" ca="1">_xlfn._xlws.PY(6,0)</f>
         <v>origin</v>
       </c>
       <c r="B23" t="str">
+        <f ca="1"/>
         <v>cylinders</v>
       </c>
       <c r="C23" t="str">
+        <f ca="1"/>
         <v>engine_size</v>
       </c>
       <c r="D23" t="str">
+        <f ca="1"/>
         <v>count</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A24" t="str">
+        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="B24">
+        <f ca="1"/>
         <v>8</v>
       </c>
       <c r="C24" t="str">
+        <f ca="1"/>
         <v>Large (8)</v>
       </c>
       <c r="D24">
+        <f ca="1"/>
         <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A25" t="str">
+        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="B25">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="C25" t="str">
+        <f ca="1"/>
         <v>Medium (5-6)</v>
       </c>
       <c r="D25">
+        <f ca="1"/>
         <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A26" t="str">
+        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="B26">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="C26" t="str">
+        <f ca="1"/>
         <v>Small (3-4)</v>
       </c>
       <c r="D26">
+        <f ca="1"/>
         <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A27" t="str">
+        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B27">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="C27" t="str">
+        <f ca="1"/>
         <v>Small (3-4)</v>
       </c>
       <c r="D27">
+        <f ca="1"/>
         <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A28" t="str">
+        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B28">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="C28" t="str">
+        <f ca="1"/>
         <v>Small (3-4)</v>
       </c>
       <c r="D28">
+        <f ca="1"/>
         <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A29" t="str">
+        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B29">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="C29" t="str">
+        <f ca="1"/>
         <v>Medium (5-6)</v>
       </c>
       <c r="D29">
+        <f ca="1"/>
         <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A30" t="str">
+        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B30">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="C30" t="str">
+        <f ca="1"/>
         <v>Medium (5-6)</v>
       </c>
       <c r="D30">
+        <f ca="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A31" t="str">
+        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B31">
+        <f ca="1"/>
         <v>3</v>
       </c>
       <c r="C31" t="str">
+        <f ca="1"/>
         <v>Small (3-4)</v>
       </c>
       <c r="D31">
+        <f ca="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A32" t="str">
+        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B32">
+        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="C32" t="str">
+        <f ca="1"/>
         <v>Medium (5-6)</v>
       </c>
       <c r="D32">
+        <f ca="1"/>
         <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A34" t="str" cm="1">
-        <f t="array" ref="A34:D38">_xlfn._xlws.PY(7,0)</f>
+        <f t="array" aca="1" ref="A34:D38" ca="1">_xlfn._xlws.PY(7,0)</f>
         <v>engine_size</v>
       </c>
       <c r="B34" t="str">
+        <f ca="1"/>
         <v>Small (3-4)</v>
       </c>
       <c r="C34" t="str">
+        <f ca="1"/>
         <v>Medium (5-6)</v>
       </c>
       <c r="D34" t="str">
+        <f ca="1"/>
         <v>Large (8)</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A35" t="str">
+        <f ca="1"/>
         <v>origin</v>
       </c>
       <c r="B35" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="C35" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="D35" t="str">
+        <f ca="1"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A36" t="str">
+        <f ca="1"/>
         <v>europe</v>
       </c>
       <c r="B36">
+        <f ca="1"/>
         <v>63</v>
       </c>
       <c r="C36">
+        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="D36">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A37" t="str">
+        <f ca="1"/>
         <v>japan</v>
       </c>
       <c r="B37">
+        <f ca="1"/>
         <v>73</v>
       </c>
       <c r="C37">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="D37">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A38" t="str">
+        <f ca="1"/>
         <v>usa</v>
       </c>
       <c r="B38">
+        <f ca="1"/>
         <v>72</v>
       </c>
       <c r="C38">
+        <f ca="1"/>
         <v>74</v>
       </c>
       <c r="D38">
+        <f ca="1"/>
         <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A42" t="str" cm="1">
-        <f t="array" ref="A42:C43">_xlfn._xlws.PY(8,0)</f>
+        <f t="array" aca="1" ref="A42:C43" ca="1">_xlfn._xlws.PY(8,0)</f>
         <v>Chi-square statistic</v>
       </c>
       <c r="B42" t="str">
+        <f ca="1"/>
         <v>p-value</v>
       </c>
       <c r="C42" t="str">
+        <f ca="1"/>
         <v>Degrees of freedom</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A43">
+        <f ca="1"/>
         <v>149.93</v>
       </c>
       <c r="B43" t="str">
+        <f ca="1"/>
         <v>0.0</v>
       </c>
       <c r="C43">
+        <f ca="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A47" t="str" cm="1">
-        <f t="array" ref="A47">_xlfn._xlws.PY(9,0)</f>
+        <f t="array" aca="1" ref="A47" ca="1">_xlfn._xlws.PY(9,0)</f>
         <v>Cramér's V: 0.43</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A51" cm="1" vm="2">
-        <f t="array" ref="A51">_xlfn._xlws.PY(10,1)</f>
+        <f t="array" aca="1" ref="A51" ca="1">_xlfn._xlws.PY(10,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A53" t="str" cm="1">
-        <f t="array" ref="A53:D54">_xlfn._xlws.PY(11,0)</f>
+        <f t="array" aca="1" ref="A53:D54" ca="1">_xlfn._xlws.PY(11,0)</f>
         <v>Original mean</v>
       </c>
       <c r="B53" t="str">
+        <f ca="1"/>
         <v>95% CI lower</v>
       </c>
       <c r="C53" t="str">
+        <f ca="1"/>
         <v>95% CI upper</v>
       </c>
       <c r="D53" t="str">
+        <f ca="1"/>
         <v>CI width</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A54">
+        <f ca="1"/>
         <v>30.45</v>
       </c>
       <c r="B54">
+        <f ca="1"/>
         <v>29.08</v>
       </c>
       <c r="C54">
+        <f ca="1"/>
         <v>31.94</v>
       </c>
       <c r="D54">
+        <f ca="1"/>
         <v>2.86</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A57" t="e" cm="1" vm="3">
-        <f t="array" ref="A57">_xlfn._xlws.PY(12,0)</f>
+        <f t="array" aca="1" ref="A57" ca="1">_xlfn._xlws.PY(12,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A71" t="str" cm="1">
-        <f t="array" ref="A71:D73">_xlfn._xlws.PY(13,0)</f>
+        <f t="array" aca="1" ref="A71:D73" ca="1">_xlfn._xlws.PY(13,0)</f>
         <v>Group</v>
       </c>
       <c r="B71" t="str">
+        <f ca="1"/>
         <v>Mean</v>
       </c>
       <c r="C71" t="str">
+        <f ca="1"/>
         <v>CI Lower (2.5%)</v>
       </c>
       <c r="D71" t="str">
+        <f ca="1"/>
         <v>CI Upper (97.5%)</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A72" t="str">
+        <f ca="1"/>
         <v>Japan</v>
       </c>
       <c r="B72" s="1">
+        <f ca="1"/>
         <v>30.450632911392404</v>
       </c>
       <c r="C72" s="1">
+        <f ca="1"/>
         <v>29.232120253164553</v>
       </c>
       <c r="D72" s="1">
+        <f ca="1"/>
         <v>31.810158227848103</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A73" t="str">
+        <f ca="1"/>
         <v>Europe</v>
       </c>
       <c r="B73" s="1">
+        <f ca="1"/>
         <v>27.89142857142857</v>
       </c>
       <c r="C73" s="1">
+        <f ca="1"/>
         <v>26.298464285714289</v>
       </c>
       <c r="D73" s="1">
+        <f ca="1"/>
         <v>29.408678571428577</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A79" t="e" cm="1" vm="4">
-        <f t="array" ref="A79">_xlfn._xlws.PY(14,0)</f>
+        <f t="array" aca="1" ref="A79" ca="1">_xlfn._xlws.PY(14,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
